--- a/Configs/GameConfig/Datas/unit.xlsx
+++ b/Configs/GameConfig/Datas/unit.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28260" windowHeight="14910"/>
+    <workbookView windowWidth="20340" windowHeight="14910"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="26">
   <si>
     <t>##var</t>
   </si>
@@ -85,6 +85,9 @@
     <t>quality</t>
   </si>
   <si>
+    <t>img_path</t>
+  </si>
+  <si>
     <t>##type</t>
   </si>
   <si>
@@ -140,16 +143,25 @@
     <t>稀有度</t>
   </si>
   <si>
+    <t>图片路径</t>
+  </si>
+  <si>
     <t>小水滴</t>
   </si>
   <si>
     <t>BLUE</t>
   </si>
   <si>
+    <t>Assets/AssetRaw/UIRaw/Atlas/Unit/Unit_1001.png</t>
+  </si>
+  <si>
     <t>小火苗</t>
   </si>
   <si>
     <t>RED</t>
+  </si>
+  <si>
+    <t>Assets/AssetRaw/UIRaw/Atlas/Unit/Unit_1002.png</t>
   </si>
 </sst>
 </file>
@@ -1104,16 +1116,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AA15"/>
+  <dimension ref="A1:Y15"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9.225" customWidth="1"/>
     <col min="2" max="2" width="6.75" customWidth="1"/>
     <col min="3" max="3" width="11" customWidth="1"/>
     <col min="4" max="6" width="12.3833333333333" customWidth="1"/>
+    <col min="7" max="7" width="45.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:27">
+    <row r="1" s="1" customFormat="1" spans="1:25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1132,7 +1145,9 @@
       <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1"/>
+      <c r="G1" s="3" t="s">
+        <v>6</v>
+      </c>
       <c r="H1"/>
       <c r="I1"/>
       <c r="J1"/>
@@ -1151,10 +1166,8 @@
       <c r="W1"/>
       <c r="X1"/>
       <c r="Y1"/>
-      <c r="Z1"/>
-      <c r="AA1"/>
-    </row>
-    <row r="2" s="1" customFormat="1" spans="1:27">
+    </row>
+    <row r="2" s="1" customFormat="1" spans="1:25">
       <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
@@ -1163,7 +1176,7 @@
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
       <c r="F2" s="3"/>
-      <c r="G2"/>
+      <c r="G2" s="3"/>
       <c r="H2"/>
       <c r="I2"/>
       <c r="J2"/>
@@ -1182,29 +1195,29 @@
       <c r="W2"/>
       <c r="X2"/>
       <c r="Y2"/>
-      <c r="Z2"/>
-      <c r="AA2"/>
-    </row>
-    <row r="3" s="2" customFormat="1" spans="1:27">
+    </row>
+    <row r="3" s="2" customFormat="1" spans="1:25">
       <c r="A3" s="4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E3" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G3" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="F3" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G3"/>
       <c r="H3"/>
       <c r="I3"/>
       <c r="J3"/>
@@ -1223,19 +1236,17 @@
       <c r="W3"/>
       <c r="X3"/>
       <c r="Y3"/>
-      <c r="Z3"/>
-      <c r="AA3"/>
-    </row>
-    <row r="4" s="2" customFormat="1" spans="1:27">
+    </row>
+    <row r="4" s="2" customFormat="1" spans="1:25">
       <c r="A4" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
       <c r="D4" s="4"/>
       <c r="E4" s="4"/>
       <c r="F4" s="4"/>
-      <c r="G4"/>
+      <c r="G4" s="4"/>
       <c r="H4"/>
       <c r="I4"/>
       <c r="J4"/>
@@ -1254,29 +1265,29 @@
       <c r="W4"/>
       <c r="X4"/>
       <c r="Y4"/>
-      <c r="Z4"/>
-      <c r="AA4"/>
-    </row>
-    <row r="5" s="1" customFormat="1" spans="1:27">
+    </row>
+    <row r="5" s="1" customFormat="1" spans="1:25">
       <c r="A5" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G5"/>
+        <v>18</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>19</v>
+      </c>
       <c r="H5"/>
       <c r="I5"/>
       <c r="J5"/>
@@ -1295,78 +1306,90 @@
       <c r="W5"/>
       <c r="X5"/>
       <c r="Y5"/>
-      <c r="Z5"/>
-      <c r="AA5"/>
-    </row>
-    <row r="6" spans="1:27">
+    </row>
+    <row r="6" spans="1:25">
       <c r="B6">
         <v>1001</v>
       </c>
       <c r="C6" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D6"/>
       <c r="E6" s="5" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="7" spans="1:27">
+        <v>21</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" spans="1:25">
       <c r="B7">
         <v>1002</v>
       </c>
       <c r="C7" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D7"/>
       <c r="E7" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="F7" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="F7" s="5" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="8" spans="1:27">
+      <c r="G7" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25">
       <c r="E8" s="5"/>
       <c r="F8" s="5"/>
-    </row>
-    <row r="9" spans="1:27">
+      <c r="G8" s="5"/>
+    </row>
+    <row r="9" spans="1:25">
       <c r="E9" s="5"/>
       <c r="F9" s="5"/>
-    </row>
-    <row r="10" spans="1:27">
+      <c r="G9" s="5"/>
+    </row>
+    <row r="10" spans="1:25">
       <c r="E10" s="5"/>
       <c r="F10" s="5"/>
-    </row>
-    <row r="11" spans="1:27">
+      <c r="G10" s="5"/>
+    </row>
+    <row r="11" spans="1:25">
       <c r="C11" s="5"/>
       <c r="D11"/>
       <c r="E11" s="5"/>
       <c r="F11" s="5"/>
-    </row>
-    <row r="12" spans="1:27">
+      <c r="G11" s="5"/>
+    </row>
+    <row r="12" spans="1:25">
       <c r="E12" s="5"/>
       <c r="F12" s="5"/>
-    </row>
-    <row r="13" spans="1:27">
+      <c r="G12" s="5"/>
+    </row>
+    <row r="13" spans="1:25">
       <c r="C13" s="5"/>
       <c r="D13" s="5"/>
       <c r="E13" s="5"/>
       <c r="F13" s="5"/>
-    </row>
-    <row r="14" spans="1:27">
+      <c r="G13" s="5"/>
+    </row>
+    <row r="14" spans="1:25">
       <c r="C14" s="5"/>
       <c r="D14" s="5"/>
       <c r="E14" s="5"/>
       <c r="F14" s="5"/>
-    </row>
-    <row r="15" spans="1:27">
+      <c r="G14" s="5"/>
+    </row>
+    <row r="15" spans="1:25">
       <c r="C15" s="5"/>
       <c r="D15" s="5"/>
       <c r="E15" s="5"/>
       <c r="F15" s="5"/>
+      <c r="G15" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
